--- a/artfynd/A 39293-2022 artfynd.xlsx
+++ b/artfynd/A 39293-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39293-2022 artfynd.xlsx
+++ b/artfynd/A 39293-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113290578</v>
+        <v>113290566</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,7 +717,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688985</v>
+        <v>688970</v>
       </c>
       <c r="R2" t="n">
         <v>7264555</v>
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113290634</v>
+        <v>113290554</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,29 +791,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688815</v>
+        <v>688965</v>
       </c>
       <c r="R3" t="n">
-        <v>7264360</v>
+        <v>7264505</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113290566</v>
+        <v>113290578</v>
       </c>
       <c r="B4" t="n">
-        <v>90279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,7 +923,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688970</v>
+        <v>688985</v>
       </c>
       <c r="R4" t="n">
         <v>7264555</v>
@@ -1005,47 +986,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113290589</v>
+        <v>113290634</v>
       </c>
       <c r="B5" t="n">
-        <v>97554</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688995</v>
+        <v>688815</v>
       </c>
       <c r="R5" t="n">
-        <v>7264555</v>
+        <v>7264360</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,16 +1094,11 @@
         <v>113290569</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1226,42 +1196,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113290554</v>
+        <v>113290620</v>
       </c>
       <c r="B7" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688965</v>
+        <v>689005</v>
       </c>
       <c r="R7" t="n">
-        <v>7264505</v>
+        <v>7264390</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,6 +1274,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>fertil!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,15 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113290620</v>
+        <v>79242679</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43258</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,30 +1317,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>201129</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689005</v>
+        <v>688978</v>
       </c>
       <c r="R8" t="n">
-        <v>7264390</v>
+        <v>7264488</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,17 +1384,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2019-08-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>fertil!</t>
+          <t>2019-08-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,15 +1405,125 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Roger Marklund, Leif Björk, Maria Marklund, Siri Björk, Jakob Wennberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fjärilar i Pite lappmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113290589</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brunmyrheden, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>688995</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7264555</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Patrik Nygren</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39293-2022 artfynd.xlsx
+++ b/artfynd/A 39293-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290566</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290554</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290578</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290634</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290620</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
           <t>Fjärilar i Pite lappmark</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79242679</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,8 +1564,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113290589</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>